--- a/output/pdf_financials_xlsx/NFI.xlsx
+++ b/output/pdf_financials_xlsx/NFI.xlsx
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>45.844</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>44.115</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>41.525</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>43.091</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46.84</v>
+        <v>45.844</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>46.502</v>
+        <v>44.115</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>45.268</v>
+        <v>41.525</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>45.792</v>
+        <v>43.091</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -1112,16 +1112,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>914.461</v>
+        <v>915.457</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1053.364</v>
+        <v>1055.751</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>69.702</v>
+        <v>73.44499999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>28.728</v>
+        <v>31.429</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -2937,37 +2937,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>30.721</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>30.696</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>73.46299999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>10.133</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>11.896</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>17.456</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>24.88</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>13.047</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>10.82</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>28.233</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>55.769</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>77.318</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>49.615</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>49.557</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>118.548</v>
       </c>
     </row>
     <row r="35">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>30.721</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>30.696</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>73.46299999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>10.133</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>11.896</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>17.456</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>24.88</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>13.047</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>10.82</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>28.233</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>55.769</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -3089,16 +3089,16 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>77.318</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>49.615</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>49.557</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>118.548</v>
       </c>
     </row>
     <row r="37">
@@ -3744,28 +3744,28 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>15.355</v>
+        <v>5.222</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>23.316</v>
+        <v>5.86</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>36.163</v>
+        <v>11.283</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>28.2</v>
+        <v>15.153</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>55.369</v>
+        <v>44.549</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>55.702</v>
+        <v>27.469</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>92.32599999999999</v>
+        <v>36.557</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>106.705</v>
+        <v>29.387</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>94.917</v>
+        <v>45.302</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>6.937</v>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -15084,7 +15084,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21954,7 +21954,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -29796,7 +29796,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -32492,7 +32492,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -68970,7 +68970,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -71148,7 +71148,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E653" s="5" t="n">

--- a/output/pdf_financials_xlsx/NFI.xlsx
+++ b/output/pdf_financials_xlsx/NFI.xlsx
@@ -1118,10 +1118,10 @@
         <v>1055.751</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>73.44499999999999</v>
+        <v>68.654</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>31.429</v>
+        <v>25.913</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         <v>-35.762</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-68.654</v>
+        <v>-26.688</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-25.913</v>
+        <v>-10.763</v>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
@@ -6861,28 +6861,28 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>15.572</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>15.866</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>15.981</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>16.007</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>18.442</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>20.465</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>20.724</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>31.553</v>
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>34.956</v>
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
@@ -6909,10 +6909,10 @@
         <v>0</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>32.348</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>29.185</v>
       </c>
     </row>
     <row r="101">
@@ -39598,7 +39598,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E321" s="5" t="n">
@@ -49812,7 +49812,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -53312,7 +53312,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -64614,7 +64614,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -69436,7 +69436,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">

--- a/output/pdf_financials_xlsx/NFI.xlsx
+++ b/output/pdf_financials_xlsx/NFI.xlsx
@@ -1112,16 +1112,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>915.457</v>
+        <v>68.64700000000001</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1055.751</v>
+        <v>77.48699999999999</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>68.654</v>
+        <v>73.629</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>25.913</v>
+        <v>34.241</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>581.402</v>
       </c>
     </row>
     <row r="57">
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>374.642</v>
       </c>
     </row>
     <row r="58">
@@ -4403,34 +4403,34 @@
         <v>389.274</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>574.491</v>
+        <v>373.408</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>559.711</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>544.361</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>569.414</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>544.4640000000001</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>926.042</v>
+        <v>0</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>894.7089999999999</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>951.01</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>1250.518</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>1177.381</v>
+        <v>0</v>
       </c>
       <c r="M59" s="1" t="inlineStr">
         <is>
@@ -4438,16 +4438,16 @@
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>1144.963</v>
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>976.377</v>
+        <v>0</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>956.954</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>857.394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -7589,16 +7589,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="L112" s="1" t="inlineStr">
         <is>
@@ -7634,13 +7634,13 @@
         <v>0</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.963</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="113">
@@ -7839,22 +7839,22 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.631</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.174</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-5.512</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.227</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="J116" s="1" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="L116" s="1" t="inlineStr">
         <is>
@@ -7875,16 +7875,16 @@
         </is>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-10.212</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-10.274</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-17.597</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-11.458</v>
       </c>
     </row>
     <row r="117">
@@ -8667,35 +8667,25 @@
       <c r="E129" s="3" t="n">
         <v>-18.653</v>
       </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F129" s="3" t="n">
+        <v>93.045</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>-29.22</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>443.562</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>-136.968</v>
       </c>
       <c r="J129" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K129" s="3" t="n">
+        <v>-83.774</v>
       </c>
       <c r="L129" s="1" t="inlineStr">
         <is>
@@ -8716,10 +8706,8 @@
       <c r="P129" s="3" t="n">
         <v>0.003</v>
       </c>
-      <c r="Q129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q129" s="3" t="n">
+        <v>-28.313</v>
       </c>
     </row>
     <row r="130">
@@ -9044,40 +9032,30 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-43.178</v>
+        <v>-46.155</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>17.726</v>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.275</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>35.161</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>33.937</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>125.008</v>
       </c>
       <c r="J135" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K135" s="3" t="n">
+        <v>104.153</v>
       </c>
       <c r="L135" s="1" t="inlineStr">
         <is>
@@ -9096,12 +9074,10 @@
         <v>-90.527</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>5.774</v>
-      </c>
-      <c r="Q135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-14.974</v>
+      </c>
+      <c r="Q135" s="3" t="n">
+        <v>173.668</v>
       </c>
     </row>
   </sheetData>
@@ -10666,7 +10642,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -13178,7 +13154,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -15972,7 +15948,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -22844,7 +22820,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -25174,7 +25150,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -27132,7 +27108,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -28088,7 +28064,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -30572,7 +30548,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -33380,7 +33356,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -36088,7 +36064,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -41182,7 +41158,11 @@
           <t>Net cash generated by operating activities</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -41842,7 +41822,11 @@
           <t>Proceeds from disposition of property, plant and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -42030,7 +42014,11 @@
           <t>Acquisition of intangible assets (note 11)</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -44666,7 +44654,11 @@
           <t>Net cash generated by (used in) operating activities ( (</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -45518,7 +45510,11 @@
           <t>Acquisition of intangible assets ( (</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -45612,7 +45608,11 @@
           <t>63 13 Proceeds from disposition of property, plant and equipment 963</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -48680,7 +48680,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -51170,7 +51174,11 @@
           <t>Net cash generated from operating activities 98,608</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -52038,7 +52046,11 @@
           <t>Acquisition of intangible assets (38)</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -52134,7 +52146,11 @@
           <t>Proceeds from disposition of property, plant and equipment 174</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -54770,7 +54786,11 @@
           <t>Net cash generated from operating activities 172,059</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>
@@ -55642,7 +55662,11 @@
           <t>Proceeds on disposition of property, plant and equipment 526</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -55740,7 +55764,11 @@
           <t>Acquisition of intangible assets (193)</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
@@ -57804,7 +57832,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
@@ -59668,7 +59700,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -60514,7 +60550,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
@@ -62340,7 +62380,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
@@ -63954,7 +63998,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E577" t="inlineStr">
         <is>
           <t>-</t>
@@ -66238,7 +66286,11 @@
           <t>Proceeds on disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D601" t="inlineStr"/>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E601" t="inlineStr">
         <is>
           <t>-</t>
@@ -66798,7 +66850,11 @@
           <t>Future income taxes (recovered)</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E607" s="5" t="n">
         <v>-2.353</v>
       </c>
@@ -68498,7 +68554,11 @@
           <t>Proceeds from disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E625" s="5" t="n">
         <v>0.03</v>
       </c>
@@ -69156,7 +69216,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D632" t="inlineStr"/>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E632" t="inlineStr">
         <is>
           <t>-</t>
@@ -71440,7 +71504,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E656" s="5" t="n">
         <v>68.64700000000001</v>
       </c>
